--- a/seat-extension/seat-template.xlsx
+++ b/seat-extension/seat-template.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -74,14 +74,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="맑은 고딕"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
+      <name val="현대산스 Text"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="현대산스 Text"/>
       <color rgb="FF0563C1"/>
       <sz val="11"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="현대산스 Text"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -124,7 +129,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -144,6 +149,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -571,66 +579,66 @@
   </cols>
   <sheetData>
     <row r="3">
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>순번</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>차종</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>동호회명</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>게시일</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>제목</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>주요내용 요약</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>온라인동향/로데이터 포함 여부</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>미포함시 누락 사유</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>https://cafe.naver.com/</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="11" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:J4"/>

--- a/seat-extension/seat-template.xlsx
+++ b/seat-extension/seat-template.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시트 위험상황 게시물" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'시트 위험상황 게시물'!$B$3:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'시트 위험상황 게시물'!$B$3:$K$4</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:J4"/>
+  <dimension ref="B3:K4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="5.5" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
@@ -576,6 +576,7 @@
     <col width="60" customWidth="1" style="6" min="8" max="8"/>
     <col width="22" bestFit="1" customWidth="1" style="6" min="9" max="9"/>
     <col width="60" bestFit="1" customWidth="1" style="6" min="10" max="10"/>
+    <col width="12" customWidth="1" style="6" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -622,6 +623,11 @@
       <c r="J3" s="7" t="inlineStr">
         <is>
           <t>미포함시 누락 사유</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>주제 관련도</t>
         </is>
       </c>
     </row>
@@ -639,9 +645,10 @@
       <c r="H4" s="11" t="n"/>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="11" t="n"/>
+      <c r="K4" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="B3:J4"/>
+  <autoFilter ref="B3:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId1"/>
   </hyperlinks>

--- a/seat-extension/seat-template.xlsx
+++ b/seat-extension/seat-template.xlsx
@@ -129,7 +129,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -166,12 +166,29 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFE00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -645,10 +662,19 @@
       <c r="H4" s="11" t="n"/>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="11" t="n"/>
-      <c r="K4" s="8" t="n"/>
+      <c r="K4" s="13" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:K4"/>
+  <conditionalFormatting sqref="K4:K5000">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.7</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="between" dxfId="1">
+      <formula>0</formula>
+      <formula>0.6999</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId1"/>
   </hyperlinks>

--- a/seat-extension/seat-template.xlsx
+++ b/seat-extension/seat-template.xlsx
@@ -129,7 +129,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -163,6 +163,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -585,84 +600,86 @@
   <dimension ref="B3:K4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="5.5" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
-    <col width="31.83203125" customWidth="1" style="6" min="4" max="4"/>
-    <col width="17.6640625" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
-    <col width="40" bestFit="1" customWidth="1" style="6" min="6" max="7"/>
-    <col width="38" customWidth="1" style="6" min="7" max="7"/>
-    <col width="60" customWidth="1" style="6" min="8" max="8"/>
-    <col width="22" bestFit="1" customWidth="1" style="6" min="9" max="9"/>
-    <col width="60" bestFit="1" customWidth="1" style="6" min="10" max="10"/>
-    <col width="12" customWidth="1" style="6" min="11" max="11"/>
+    <col width="2" customWidth="1" style="6" min="1" max="1"/>
+    <col width="6" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
+    <col width="7" customWidth="1" style="6" min="3" max="3"/>
+    <col width="22" customWidth="1" style="6" min="4" max="4"/>
+    <col width="12" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="56" bestFit="1" customWidth="1" style="6" min="6" max="7"/>
+    <col width="46" customWidth="1" style="6" min="7" max="7"/>
+    <col width="68" customWidth="1" style="6" min="8" max="8"/>
+    <col width="14" bestFit="1" customWidth="1" style="6" min="9" max="9"/>
+    <col width="80" bestFit="1" customWidth="1" style="6" min="10" max="10"/>
+    <col width="11" customWidth="1" style="6" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="B3" s="7" t="inlineStr">
+    <row r="3" ht="36" customHeight="1" s="6">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>순번</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>차종</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>동호회명</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>게시일</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>제목</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>주요내용 요약</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>온라인동향/로데이터 포함 여부</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>미포함시 누락 사유</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>주제 관련도</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="10" t="n"/>
+    <row r="4" ht="66" customHeight="1" s="6">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="16" t="n"/>
       <c r="F4" s="11" t="n"/>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>https://cafe.naver.com/</t>
         </is>
       </c>
       <c r="H4" s="11" t="n"/>
-      <c r="I4" s="8" t="n"/>
+      <c r="I4" s="15" t="n"/>
       <c r="J4" s="11" t="n"/>
-      <c r="K4" s="13" t="n"/>
+      <c r="K4" s="18" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:K4"/>
